--- a/public/templates/teacher.xlsx
+++ b/public/templates/teacher.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="111">
   <si>
     <t>STT</t>
   </si>
@@ -42,95 +42,323 @@
     <t>Mô tả</t>
   </si>
   <si>
-    <t>CNTT03</t>
-  </si>
-  <si>
-    <t>CNTT04</t>
-  </si>
-  <si>
-    <t>CNTT05</t>
-  </si>
-  <si>
-    <t>CNPM01</t>
-  </si>
-  <si>
-    <t>CNPM02</t>
-  </si>
-  <si>
-    <t>CNPM03</t>
-  </si>
-  <si>
-    <t>CNPM04</t>
-  </si>
-  <si>
-    <t>CNPM05</t>
-  </si>
-  <si>
-    <t>MMT01</t>
-  </si>
-  <si>
-    <t>MMT02</t>
-  </si>
-  <si>
-    <t>MMT03</t>
-  </si>
-  <si>
-    <t>MMT04</t>
-  </si>
-  <si>
-    <t>MMT05</t>
-  </si>
-  <si>
-    <t>TTNT01</t>
-  </si>
-  <si>
-    <t>TTNT02</t>
-  </si>
-  <si>
-    <t>TTNT03</t>
-  </si>
-  <si>
-    <t>TTNT04</t>
-  </si>
-  <si>
     <t>TOT07</t>
   </si>
   <si>
     <t>TOT10</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguyễn Trọng Kương </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nguyễn Thị Lan </t>
-  </si>
-  <si>
-    <t xml:space="preserve">tot07@gv.vnua.du.vn </t>
-  </si>
-  <si>
-    <t xml:space="preserve">tot10@gv.vnua.du.vn </t>
-  </si>
-  <si>
-    <t>0912121212</t>
-  </si>
-  <si>
     <t>Web</t>
   </si>
   <si>
-    <t>Ứng dụng</t>
-  </si>
-  <si>
-    <t>Website bán đồ cói</t>
-  </si>
-  <si>
-    <t>Ứng dụng đặt phòng khách sạn</t>
+    <t>AI</t>
+  </si>
+  <si>
+    <t>Web bán điện thoại</t>
+  </si>
+  <si>
+    <t>AI nhận diện khuôn mặt</t>
+  </si>
+  <si>
+    <t>Nguyễn Trọng Kương</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Lan</t>
+  </si>
+  <si>
+    <t>Bộ môn</t>
+  </si>
+  <si>
+    <t>CNPM</t>
+  </si>
+  <si>
+    <t>KHMT</t>
+  </si>
+  <si>
+    <t>Hoàng Thị Hà</t>
+  </si>
+  <si>
+    <t>Trần Trung Hiếu</t>
+  </si>
+  <si>
+    <t>Đỗ Thị Nhâm</t>
+  </si>
+  <si>
+    <t>Lê Thị Nhung</t>
+  </si>
+  <si>
+    <t>Ngô Công Thắng</t>
+  </si>
+  <si>
+    <t>Lê Thị Minh Thùy</t>
+  </si>
+  <si>
+    <t>Phan Trọng Tiến</t>
+  </si>
+  <si>
+    <t>Phạm Quang Dũng</t>
+  </si>
+  <si>
+    <t>Trần Vũ Hà</t>
+  </si>
+  <si>
+    <t>Nguyễn Hữu Hải</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Thảo</t>
+  </si>
+  <si>
+    <t>Mạng &amp; HTTT</t>
+  </si>
+  <si>
+    <t>Phạm Thị Lan Anh</t>
+  </si>
+  <si>
+    <t>Đoàn Thị Thu Hà</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn Hoàng</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Huyền</t>
+  </si>
+  <si>
+    <t>Trần Thị Thu Huyền</t>
+  </si>
+  <si>
+    <t>Vũ Thị Lưu</t>
+  </si>
+  <si>
+    <t>ngtlan@vnua.edu.vn</t>
+  </si>
+  <si>
+    <t>CNP11</t>
+  </si>
+  <si>
+    <t>ltmthuy@vnua.edu.vn</t>
+  </si>
+  <si>
+    <t>MTI12</t>
+  </si>
+  <si>
+    <t>MTI01</t>
+  </si>
+  <si>
+    <t>ttthuyen@vnua.edu.vn</t>
+  </si>
+  <si>
+    <t>MTI08</t>
+  </si>
+  <si>
+    <t>tvha@vnua.edu.vn</t>
+  </si>
+  <si>
+    <t>CNP09</t>
+  </si>
+  <si>
+    <t>tthieu@vnua.edu.vn</t>
+  </si>
+  <si>
+    <t>CNP05</t>
+  </si>
+  <si>
+    <t>ptgtien@vnua.edu.vn</t>
+  </si>
+  <si>
+    <t>TOA27</t>
+  </si>
+  <si>
+    <t>nhhai@vnua.edu.vn</t>
+  </si>
+  <si>
+    <t>CNP07</t>
+  </si>
+  <si>
+    <t>htha@vnua.edu.vn</t>
+  </si>
+  <si>
+    <t>MTI07</t>
+  </si>
+  <si>
+    <t>dttha@vnua.edu.vn</t>
+  </si>
+  <si>
+    <t>MTI11</t>
+  </si>
+  <si>
+    <t>nvhoang@vnua.edu.vn</t>
+  </si>
+  <si>
+    <t>vtluu@vnua.edu.vn</t>
+  </si>
+  <si>
+    <t>MTI05</t>
+  </si>
+  <si>
+    <t>pqdung@vnua.edu.vn</t>
+  </si>
+  <si>
+    <t>MTI13</t>
+  </si>
+  <si>
+    <t>ntthao81@vnua.edu.vn</t>
+  </si>
+  <si>
+    <t>MTI10</t>
+  </si>
+  <si>
+    <t>nthuyen@vnua.edu.vn</t>
+  </si>
+  <si>
+    <t>MTI15</t>
+  </si>
+  <si>
+    <t>ptlanh@vnua.edu.vn</t>
+  </si>
+  <si>
+    <t>CNP03</t>
+  </si>
+  <si>
+    <t>dtnham@vnua.edu.vn</t>
+  </si>
+  <si>
+    <t>ntkuong@vnua.edu.vn</t>
+  </si>
+  <si>
+    <t>CNP12</t>
+  </si>
+  <si>
+    <t>ltnhung@vnua.edu.vn</t>
+  </si>
+  <si>
+    <t>CNP02</t>
+  </si>
+  <si>
+    <t>ncthang@vnua.edu.vn</t>
+  </si>
+  <si>
+    <t>0916 893 835</t>
+  </si>
+  <si>
+    <t>0975 276 080</t>
+  </si>
+  <si>
+    <t>0975 500 438</t>
+  </si>
+  <si>
+    <t>0917 885 996</t>
+  </si>
+  <si>
+    <t>0912 817 498</t>
+  </si>
+  <si>
+    <t>0915 577 025</t>
+  </si>
+  <si>
+    <t>0963 493 598</t>
+  </si>
+  <si>
+    <t>0986 511 750</t>
+  </si>
+  <si>
+    <t>0912 647 047</t>
+  </si>
+  <si>
+    <t>0972 016 961</t>
+  </si>
+  <si>
+    <t>0374 168 288</t>
+  </si>
+  <si>
+    <t>0979 430 884</t>
+  </si>
+  <si>
+    <t>0983 199 466</t>
+  </si>
+  <si>
+    <t>0904 240 676</t>
+  </si>
+  <si>
+    <t>0978 278 035</t>
+  </si>
+  <si>
+    <t>0349 696 634</t>
+  </si>
+  <si>
+    <t>0812 659 928</t>
+  </si>
+  <si>
+    <t>0971 027 735</t>
+  </si>
+  <si>
+    <t>0977 832 125</t>
+  </si>
+  <si>
+    <t>Xây dựng Website quản lý đặt bàn online cho nhà hàng</t>
+  </si>
+  <si>
+    <t>Xây dựng ứng dụng bầu cử trực tuyến trên nền tảng Ethereum</t>
+  </si>
+  <si>
+    <t>Blockchain</t>
+  </si>
+  <si>
+    <t>Xây dựng phần mềm quản lý giải bóng đá</t>
+  </si>
+  <si>
+    <t>Quản Lý Bán Hàng Cho Cửa Hàng Đồ Uống</t>
+  </si>
+  <si>
+    <t>Xây dựng phần mềm quản lý thực tập nghề nghiệp</t>
+  </si>
+  <si>
+    <t>Xây dựng ứng dụng web bán đồ điện tử</t>
+  </si>
+  <si>
+    <t>Nhận diện khuôn mặt trong ảnh sử dụng kỹ thuật học máy</t>
+  </si>
+  <si>
+    <t>Xây dựng ứng dụng web đặt vé xem phim</t>
+  </si>
+  <si>
+    <t>Website bán phụ kiện nội thất ô tô</t>
+  </si>
+  <si>
+    <t>Tìm hiểu các kĩ thuật lọc nhiễu và ứng dụng trong xử lý dữ liệu</t>
+  </si>
+  <si>
+    <t>Khoa học &amp; Xủ lý dữ liệu</t>
+  </si>
+  <si>
+    <t>HỆ THỐNG QUẢN LÝ GIÁO DỤC - ISTUDY</t>
+  </si>
+  <si>
+    <t>Xây dựng trang web bán nông sản thuần hữu cơ có tích hợp trí tuệ nhân tạo</t>
+  </si>
+  <si>
+    <t>Xây dựng website đọc truyện</t>
+  </si>
+  <si>
+    <t>Kiểm thử Phần mềm Quản lý tổng thể nông nghiệp</t>
+  </si>
+  <si>
+    <t>Kiểm thử</t>
+  </si>
+  <si>
+    <t>Xây dựng website ôn thi trắc nghiệm online</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiểm thử app EcoOne chức năng: -Hiện thị giao diện mMenu lên ứng dụng EcoOne. </t>
+  </si>
+  <si>
+    <t>Web đọc sách, truyện</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -158,16 +386,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -177,6 +397,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -205,25 +431,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -231,11 +451,15 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -514,19 +738,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="15.28515625" customWidth="1"/>
     <col min="3" max="3" width="20.42578125" customWidth="1"/>
     <col min="4" max="4" width="26.7109375" customWidth="1"/>
-    <col min="5" max="5" width="22.42578125" style="10" customWidth="1"/>
+    <col min="5" max="5" width="22.42578125" style="6" customWidth="1"/>
     <col min="6" max="6" width="17.5703125" customWidth="1"/>
-    <col min="7" max="7" width="27.5703125" customWidth="1"/>
+    <col min="7" max="7" width="36.5703125" customWidth="1"/>
+    <col min="8" max="8" width="72" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -537,301 +762,559 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5">
+      <c r="I1" s="7"/>
+      <c r="J1" s="8"/>
+    </row>
+    <row r="2" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="I2" s="7"/>
+      <c r="J2" s="8"/>
+    </row>
+    <row r="3" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="I3" s="7"/>
+      <c r="J3" s="8"/>
+    </row>
+    <row r="4" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="I4" s="7"/>
+      <c r="J4" s="9"/>
+    </row>
+    <row r="5" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="I5" s="7"/>
+      <c r="J5" s="8"/>
+    </row>
+    <row r="6" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I6" s="7"/>
+      <c r="J6" s="8"/>
+    </row>
+    <row r="7" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="I7" s="7"/>
+      <c r="J7" s="8"/>
+    </row>
+    <row r="8" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D8" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I8" s="7"/>
+      <c r="J8" s="8"/>
+    </row>
+    <row r="9" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I9" s="7"/>
+      <c r="J9" s="8"/>
+    </row>
+    <row r="10" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D10" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I10" s="7"/>
+      <c r="J10" s="8"/>
+    </row>
+    <row r="11" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I11" s="7"/>
+      <c r="J11" s="8"/>
+    </row>
+    <row r="12" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I12" s="7"/>
+      <c r="J12" s="8"/>
+    </row>
+    <row r="13" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I13" s="7"/>
+      <c r="J13" s="8"/>
+    </row>
+    <row r="14" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="D14" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I14" s="7"/>
+      <c r="J14" s="8"/>
+    </row>
+    <row r="15" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I15" s="7"/>
+      <c r="J15" s="8"/>
+    </row>
+    <row r="16" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I16" s="7"/>
+      <c r="J16" s="8"/>
+    </row>
+    <row r="17" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="D17" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I17" s="7"/>
+      <c r="J17" s="8"/>
+    </row>
+    <row r="18" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="D18" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="I18" s="7"/>
+      <c r="J18" s="8"/>
+    </row>
+    <row r="19" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="I19" s="7"/>
+      <c r="J19" s="8"/>
+    </row>
+    <row r="20" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="5">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="I4" s="3"/>
-    </row>
-    <row r="5" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-    </row>
-    <row r="6" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5">
-        <v>5</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-    </row>
-    <row r="7" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="5">
-        <v>6</v>
-      </c>
-      <c r="B7" s="4" t="s">
+      <c r="D20" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-    </row>
-    <row r="8" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="5">
-        <v>7</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-    </row>
-    <row r="9" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="5">
-        <v>8</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-    </row>
-    <row r="10" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="5">
-        <v>9</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-    </row>
-    <row r="11" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="5">
-        <v>10</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-    </row>
-    <row r="12" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="5">
-        <v>11</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-    </row>
-    <row r="13" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="5">
-        <v>12</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-    </row>
-    <row r="14" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="5">
-        <v>13</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-    </row>
-    <row r="15" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="5">
-        <v>14</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-    </row>
-    <row r="16" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="5">
-        <v>15</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-    </row>
-    <row r="17" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="5">
-        <v>16</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-    </row>
-    <row r="18" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="5">
-        <v>17</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-    </row>
-    <row r="19" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="5">
-        <v>18</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-    </row>
-    <row r="20" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="5">
-        <v>19</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-    </row>
+      <c r="H20" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="I20" s="7"/>
+      <c r="J20" s="8"/>
+    </row>
+    <row r="21" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1"/>
-    <hyperlink ref="D3" r:id="rId2"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/public/templates/teacher.xlsx
+++ b/public/templates/teacher.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="87">
   <si>
     <t>STT</t>
   </si>
@@ -36,30 +36,12 @@
     <t>Số điện thoại</t>
   </si>
   <si>
-    <t>Hướng đề tài</t>
-  </si>
-  <si>
-    <t>Mô tả</t>
-  </si>
-  <si>
     <t>TOT07</t>
   </si>
   <si>
     <t>TOT10</t>
   </si>
   <si>
-    <t>Web</t>
-  </si>
-  <si>
-    <t>AI</t>
-  </si>
-  <si>
-    <t>Web bán điện thoại</t>
-  </si>
-  <si>
-    <t>AI nhận diện khuôn mặt</t>
-  </si>
-  <si>
     <t>Nguyễn Trọng Kương</t>
   </si>
   <si>
@@ -294,71 +276,20 @@
     <t>0977 832 125</t>
   </si>
   <si>
-    <t>Xây dựng Website quản lý đặt bàn online cho nhà hàng</t>
-  </si>
-  <si>
-    <t>Xây dựng ứng dụng bầu cử trực tuyến trên nền tảng Ethereum</t>
-  </si>
-  <si>
-    <t>Blockchain</t>
-  </si>
-  <si>
-    <t>Xây dựng phần mềm quản lý giải bóng đá</t>
-  </si>
-  <si>
-    <t>Quản Lý Bán Hàng Cho Cửa Hàng Đồ Uống</t>
-  </si>
-  <si>
-    <t>Xây dựng phần mềm quản lý thực tập nghề nghiệp</t>
-  </si>
-  <si>
-    <t>Xây dựng ứng dụng web bán đồ điện tử</t>
-  </si>
-  <si>
-    <t>Nhận diện khuôn mặt trong ảnh sử dụng kỹ thuật học máy</t>
-  </si>
-  <si>
-    <t>Xây dựng ứng dụng web đặt vé xem phim</t>
-  </si>
-  <si>
-    <t>Website bán phụ kiện nội thất ô tô</t>
-  </si>
-  <si>
-    <t>Tìm hiểu các kĩ thuật lọc nhiễu và ứng dụng trong xử lý dữ liệu</t>
-  </si>
-  <si>
-    <t>Khoa học &amp; Xủ lý dữ liệu</t>
-  </si>
-  <si>
-    <t>HỆ THỐNG QUẢN LÝ GIÁO DỤC - ISTUDY</t>
-  </si>
-  <si>
-    <t>Xây dựng trang web bán nông sản thuần hữu cơ có tích hợp trí tuệ nhân tạo</t>
-  </si>
-  <si>
-    <t>Xây dựng website đọc truyện</t>
-  </si>
-  <si>
-    <t>Kiểm thử Phần mềm Quản lý tổng thể nông nghiệp</t>
-  </si>
-  <si>
-    <t>Kiểm thử</t>
-  </si>
-  <si>
-    <t>Xây dựng website ôn thi trắc nghiệm online</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kiểm thử app EcoOne chức năng: -Hiện thị giao diện mMenu lên ứng dụng EcoOne. </t>
-  </si>
-  <si>
-    <t>Web đọc sách, truyện</t>
+    <t>Ngày sinh</t>
+  </si>
+  <si>
+    <t>10/10/2005</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="173" formatCode="[$-1010000]d/m/yyyy;@"/>
+  </numFmts>
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -386,6 +317,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -407,7 +351,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -430,11 +374,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -458,9 +415,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="2"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -738,20 +719,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="15.28515625" customWidth="1"/>
     <col min="3" max="3" width="20.42578125" customWidth="1"/>
     <col min="4" max="4" width="26.7109375" customWidth="1"/>
-    <col min="5" max="5" width="22.42578125" style="6" customWidth="1"/>
-    <col min="6" max="6" width="17.5703125" customWidth="1"/>
-    <col min="7" max="7" width="36.5703125" customWidth="1"/>
-    <col min="8" max="8" width="72" customWidth="1"/>
+    <col min="5" max="5" width="26.7109375" style="19" customWidth="1"/>
+    <col min="6" max="6" width="22.42578125" style="6" customWidth="1"/>
+    <col min="7" max="7" width="17.5703125" customWidth="1"/>
+    <col min="8" max="8" width="36.5703125" customWidth="1"/>
+    <col min="9" max="9" width="72" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -762,557 +744,533 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="7"/>
-      <c r="J1" s="8"/>
-    </row>
-    <row r="2" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I1" s="13"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="8"/>
+    </row>
+    <row r="2" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="I2" s="7"/>
-      <c r="J2" s="8"/>
-    </row>
-    <row r="3" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="I2" s="12"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="8"/>
+    </row>
+    <row r="3" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="I3" s="7"/>
-      <c r="J3" s="8"/>
-    </row>
-    <row r="4" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="I3" s="12"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="8"/>
+    </row>
+    <row r="4" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="I4" s="7"/>
-      <c r="J4" s="9"/>
-    </row>
-    <row r="5" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="I4" s="12"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="9"/>
+    </row>
+    <row r="5" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G5" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="I5" s="7"/>
-      <c r="J5" s="8"/>
-    </row>
-    <row r="6" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I5" s="12"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="8"/>
+    </row>
+    <row r="6" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G6" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="I6" s="7"/>
-      <c r="J6" s="8"/>
-    </row>
-    <row r="7" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I6" s="12"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="8"/>
+    </row>
+    <row r="7" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="I7" s="7"/>
-      <c r="J7" s="8"/>
-    </row>
-    <row r="8" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="I7" s="12"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="8"/>
+    </row>
+    <row r="8" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="I8" s="7"/>
-      <c r="J8" s="8"/>
-    </row>
-    <row r="9" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="I8" s="12"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="8"/>
+    </row>
+    <row r="9" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="I9" s="7"/>
-      <c r="J9" s="8"/>
-    </row>
-    <row r="10" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="I9" s="12"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="8"/>
+    </row>
+    <row r="10" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I10" s="7"/>
-      <c r="J10" s="8"/>
-    </row>
-    <row r="11" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I10" s="12"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="8"/>
+    </row>
+    <row r="11" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="I11" s="7"/>
-      <c r="J11" s="8"/>
-    </row>
-    <row r="12" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I11" s="12"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="8"/>
+    </row>
+    <row r="12" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="D12" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I12" s="7"/>
-      <c r="J12" s="8"/>
-    </row>
-    <row r="13" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="I12" s="12"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="8"/>
+    </row>
+    <row r="13" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="D13" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="I13" s="7"/>
-      <c r="J13" s="8"/>
-    </row>
-    <row r="14" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="I13" s="12"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="8"/>
+    </row>
+    <row r="14" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I14" s="7"/>
-      <c r="J14" s="8"/>
-    </row>
-    <row r="15" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="I14" s="12"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="8"/>
+    </row>
+    <row r="15" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="I15" s="7"/>
-      <c r="J15" s="8"/>
-    </row>
-    <row r="16" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="I15" s="12"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="8"/>
+    </row>
+    <row r="16" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I16" s="7"/>
-      <c r="J16" s="8"/>
-    </row>
-    <row r="17" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I16" s="12"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="8"/>
+    </row>
+    <row r="17" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="I17" s="7"/>
-      <c r="J17" s="8"/>
-    </row>
-    <row r="18" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="I17" s="12"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="8"/>
+    </row>
+    <row r="18" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="I18" s="7"/>
-      <c r="J18" s="8"/>
-    </row>
-    <row r="19" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="E18" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="I18" s="12"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="8"/>
+    </row>
+    <row r="19" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="I19" s="7"/>
-      <c r="J19" s="8"/>
-    </row>
-    <row r="20" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="E19" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="I19" s="12"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="8"/>
+    </row>
+    <row r="20" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="I20" s="7"/>
-      <c r="J20" s="8"/>
-    </row>
-    <row r="21" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+        <v>11</v>
+      </c>
+      <c r="E20" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="I20" s="12"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="8"/>
+    </row>
+    <row r="21" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="14"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="11"/>
+    </row>
+    <row r="22" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I22" s="8"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I23" s="8"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/public/templates/teacher.xlsx
+++ b/public/templates/teacher.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="91">
   <si>
     <t>STT</t>
   </si>
@@ -219,67 +219,83 @@
     <t>ncthang@vnua.edu.vn</t>
   </si>
   <si>
-    <t>0916 893 835</t>
-  </si>
-  <si>
-    <t>0975 276 080</t>
-  </si>
-  <si>
-    <t>0975 500 438</t>
-  </si>
-  <si>
-    <t>0917 885 996</t>
-  </si>
-  <si>
-    <t>0912 817 498</t>
-  </si>
-  <si>
-    <t>0915 577 025</t>
-  </si>
-  <si>
-    <t>0963 493 598</t>
-  </si>
-  <si>
-    <t>0986 511 750</t>
-  </si>
-  <si>
-    <t>0912 647 047</t>
-  </si>
-  <si>
-    <t>0972 016 961</t>
-  </si>
-  <si>
-    <t>0374 168 288</t>
-  </si>
-  <si>
-    <t>0979 430 884</t>
-  </si>
-  <si>
-    <t>0983 199 466</t>
-  </si>
-  <si>
-    <t>0904 240 676</t>
-  </si>
-  <si>
-    <t>0978 278 035</t>
-  </si>
-  <si>
-    <t>0349 696 634</t>
-  </si>
-  <si>
-    <t>0812 659 928</t>
-  </si>
-  <si>
-    <t>0971 027 735</t>
-  </si>
-  <si>
-    <t>0977 832 125</t>
-  </si>
-  <si>
     <t>Ngày sinh</t>
   </si>
   <si>
     <t>10/10/2005</t>
+  </si>
+  <si>
+    <t>Kiểu số nguyên
+(Bắt buộc)</t>
+  </si>
+  <si>
+    <t>Kiểu chuỗi/ 50
+(Bắt buộc)</t>
+  </si>
+  <si>
+    <t>Kiểu chuỗi/ 255
+(Bắt buộc)</t>
+  </si>
+  <si>
+    <t>dd/MM/yyyy
+(Bắt buộc)</t>
+  </si>
+  <si>
+    <t>0916893835</t>
+  </si>
+  <si>
+    <t>0975276080</t>
+  </si>
+  <si>
+    <t>0975500438</t>
+  </si>
+  <si>
+    <t>0917885996</t>
+  </si>
+  <si>
+    <t>0912817498</t>
+  </si>
+  <si>
+    <t>0915577025</t>
+  </si>
+  <si>
+    <t>0963493598</t>
+  </si>
+  <si>
+    <t>0986511750</t>
+  </si>
+  <si>
+    <t>0912647047</t>
+  </si>
+  <si>
+    <t>0972016961</t>
+  </si>
+  <si>
+    <t>0374168288</t>
+  </si>
+  <si>
+    <t>0979430884</t>
+  </si>
+  <si>
+    <t>0983199466</t>
+  </si>
+  <si>
+    <t>0904240676</t>
+  </si>
+  <si>
+    <t>0978278035</t>
+  </si>
+  <si>
+    <t>0349696634</t>
+  </si>
+  <si>
+    <t>0812659928</t>
+  </si>
+  <si>
+    <t>0971027735</t>
+  </si>
+  <si>
+    <t>0977832125</t>
   </si>
 </sst>
 </file>
@@ -287,7 +303,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="173" formatCode="[$-1010000]d/m/yyyy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-1010000]d/m/yyyy;@"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -391,7 +407,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -432,10 +448,15 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -719,10 +740,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="11.28515625" customWidth="1"/>
     <col min="2" max="2" width="15.28515625" customWidth="1"/>
     <col min="3" max="3" width="20.42578125" customWidth="1"/>
     <col min="4" max="4" width="26.7109375" customWidth="1"/>
@@ -733,157 +754,157 @@
     <col min="9" max="9" width="72" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:11" s="21" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="E1" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="G1" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="22"/>
+    </row>
+    <row r="2" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="E2" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="13"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="8"/>
-    </row>
-    <row r="2" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="20" t="s">
-        <v>86</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="I2" s="12"/>
+      <c r="I2" s="13"/>
       <c r="J2" s="7"/>
       <c r="K2" s="8"/>
     </row>
     <row r="3" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="I3" s="12"/>
       <c r="J3" s="7"/>
       <c r="K3" s="8"/>
     </row>
-    <row r="4" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>10</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="I4" s="12"/>
       <c r="J4" s="7"/>
-      <c r="K4" s="9"/>
-    </row>
-    <row r="5" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K4" s="8"/>
+    </row>
+    <row r="5" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>10</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="I5" s="12"/>
       <c r="J5" s="7"/>
-      <c r="K5" s="8"/>
+      <c r="K5" s="9"/>
     </row>
     <row r="6" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>10</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="I6" s="12"/>
       <c r="J6" s="7"/>
@@ -891,25 +912,25 @@
     </row>
     <row r="7" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>10</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I7" s="12"/>
       <c r="J7" s="7"/>
@@ -917,25 +938,25 @@
     </row>
     <row r="8" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>10</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="I8" s="12"/>
       <c r="J8" s="7"/>
@@ -943,25 +964,25 @@
     </row>
     <row r="9" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="I9" s="12"/>
       <c r="J9" s="7"/>
@@ -969,25 +990,25 @@
     </row>
     <row r="10" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>23</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="I10" s="12"/>
       <c r="J10" s="7"/>
@@ -995,25 +1016,25 @@
     </row>
     <row r="11" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>23</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="I11" s="12"/>
       <c r="J11" s="7"/>
@@ -1021,25 +1042,25 @@
     </row>
     <row r="12" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>23</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="I12" s="12"/>
       <c r="J12" s="7"/>
@@ -1047,25 +1068,25 @@
     </row>
     <row r="13" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>23</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="I13" s="12"/>
       <c r="J13" s="7"/>
@@ -1073,25 +1094,25 @@
     </row>
     <row r="14" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>53</v>
+        <v>6</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>23</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="I14" s="12"/>
       <c r="J14" s="7"/>
@@ -1099,25 +1120,25 @@
     </row>
     <row r="15" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>11</v>
+        <v>22</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>23</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I15" s="12"/>
       <c r="J15" s="7"/>
@@ -1125,25 +1146,25 @@
     </row>
     <row r="16" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I16" s="12"/>
       <c r="J16" s="7"/>
@@ -1151,25 +1172,25 @@
     </row>
     <row r="17" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D17" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E17" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G17" s="5" t="s">
         <v>86</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>81</v>
       </c>
       <c r="I17" s="12"/>
       <c r="J17" s="7"/>
@@ -1177,25 +1198,25 @@
     </row>
     <row r="18" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D18" s="10" t="s">
         <v>11</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="I18" s="12"/>
       <c r="J18" s="7"/>
@@ -1203,25 +1224,25 @@
     </row>
     <row r="19" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D19" s="10" t="s">
         <v>11</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="I19" s="12"/>
       <c r="J19" s="7"/>
@@ -1229,47 +1250,73 @@
     </row>
     <row r="20" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D20" s="10" t="s">
         <v>11</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="I20" s="12"/>
       <c r="J20" s="7"/>
       <c r="K20" s="8"/>
     </row>
-    <row r="21" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="14"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="17"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="8"/>
-      <c r="J21" s="11"/>
-    </row>
-    <row r="22" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
+        <v>19</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="I21" s="12"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="8"/>
+    </row>
+    <row r="22" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="14"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="12"/>
       <c r="I22" s="8"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J22" s="11"/>
+    </row>
+    <row r="23" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I23" s="8"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I24" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
